--- a/artfynd/A 23879-2024 artfynd.xlsx
+++ b/artfynd/A 23879-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,55 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>62816782</v>
+        <v>69532226</v>
       </c>
       <c r="B2" t="n">
-        <v>89350</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75390</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5445</v>
+        <v>1458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Grå skärelav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Dendrographa decolorans</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Turner &amp; Borrer ex Sm.) Ertz &amp; Tehler</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Strömsrum öster om, Sm</t>
+          <t>Kalmar län (lokalnamn saknas), Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>587378.0281307235</v>
+        <v>587421</v>
       </c>
       <c r="R2" t="n">
-        <v>6311344.917695691</v>
+        <v>6311238</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -747,22 +740,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2016-10-05</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2006-11-24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2016-10-05</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2006-11-24</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Kalmar läns trädinventering, Observatör Martin Hägerås</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,22 +759,361 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>skogsek</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Thomas Johansson</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Via Thomas Johansson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Trädinventeringen i Kalmar län</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>62816782</v>
+      </c>
+      <c r="B3" t="n">
+        <v>91867</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>5445</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Ekticka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Fomitiporia robusta</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Strömsrum öster om, Sm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>587378</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6311345</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Ålem</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2016-10-05</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2016-10-05</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Karolin Ring</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>Karolin Ring</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>62816787</v>
+      </c>
+      <c r="B4" t="n">
+        <v>91867</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>5445</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Ekticka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Fomitiporia robusta</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Strösmrum öster om, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>587376</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6311321</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ålem</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2016-10-05</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2016-10-05</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Karolin Ring</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Karolin Ring</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>69532227</v>
+      </c>
+      <c r="B5" t="n">
+        <v>83290</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6439</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Gulnål</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Chaenotheca brachypoda</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Kalmar län (lokalnamn saknas), Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>587421</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6311238</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ålem</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2006-11-24</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2006-11-24</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Kalmar läns trädinventering, Observatör Martin Hägerås</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>skogsek</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Thomas Johansson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Via Thomas Johansson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Trädinventeringen i Kalmar län</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 23879-2024 artfynd.xlsx
+++ b/artfynd/A 23879-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -793,6 +798,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69532226</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -893,6 +903,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62816782</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62816787</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1114,8 +1134,19 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69532227</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>